--- a/scripts/cases/igtopt_bat4b24/bat4b24.xlsx
+++ b/scripts/cases/igtopt_bat4b24/bat4b24.xlsx
@@ -15,7 +15,7 @@
     <sheet name="generator_array" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="demand_array" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="line_array" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="batterie_array" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="battery_array" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="generator_profile_array" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Demand@lmax" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="GeneratorProfile@profile" sheetId="12" state="visible" r:id="rId12"/>

--- a/scripts/cases/igtopt_bat4b24/bat4b24.xlsx
+++ b/scripts/cases/igtopt_bat4b24/bat4b24.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="options" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="block_array" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="stage_array" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="scenario_array" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="bus_array" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="generator_array" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="demand_array" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="line_array" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="battery_array" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="generator_profile_array" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Demand@lmax" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="GeneratorProfile@profile" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="options" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_array" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stage_array" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="scenario_array" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bus_array" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="generator_array" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="demand_array" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="line_array" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="battery_array" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="generator_profile_array" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand@lmax" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GeneratorProfile@profile" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>gcost</t>
+          <t>discharge_cost</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
